--- a/data/trans_camb/IP42B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 22,77</t>
+          <t>-1,3; 21,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,54; 6,85</t>
+          <t>-11,02; 5,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,58; 23,94</t>
+          <t>1,71; 25,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 19,8</t>
+          <t>-3,21; 19,06</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,98; 20,06</t>
+          <t>3,7; 20,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 11,16</t>
+          <t>-3,63; 10,27</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; —</t>
+          <t>-3,53; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,77; —</t>
+          <t>-54,87; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,06; 22,78</t>
+          <t>4,47; 24,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 10,06</t>
+          <t>-3,89; 10,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 19,66</t>
+          <t>2,44; 19,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 4,81</t>
+          <t>-6,75; 4,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 18,76</t>
+          <t>6,02; 18,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 5,32</t>
+          <t>-3,33; 5,76</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,71; 1596,69</t>
+          <t>24,3; 1564,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 750,91</t>
+          <t>-70,21; 765,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 1321,27</t>
+          <t>5,36; 1292,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-85,23; 354,54</t>
+          <t>-84,31; 353,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,18; 786,47</t>
+          <t>63,83; 890,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,41; 232,75</t>
+          <t>-52,58; 268,12</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 8,65</t>
+          <t>-24,65; 8,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 5,51</t>
+          <t>-27,57; 5,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,15; 9,61</t>
+          <t>-19,43; 11,54</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-26,38; -1,28</t>
+          <t>-28,53; -1,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 5,09</t>
+          <t>-16,84; 6,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,5; -1,88</t>
+          <t>-22,58; -2,59</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,64; 194,85</t>
+          <t>-80,99; 206,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,58; 174,62</t>
+          <t>-87,26; 165,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 96,36</t>
+          <t>-70,43; 123,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 4,52</t>
+          <t>-90,95; -1,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,23; 56,99</t>
+          <t>-65,67; 70,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,06; -9,47</t>
+          <t>-82,97; -12,23</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 17,34</t>
+          <t>-6,03; 18,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,83; 12,08</t>
+          <t>-9,93; 11,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 14,11</t>
+          <t>-3,43; 14,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 13,18</t>
+          <t>-4,05; 12,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 13,0</t>
+          <t>-2,7; 12,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 9,65</t>
+          <t>-3,8; 8,98</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-40,13; 247,44</t>
+          <t>-39,09; 258,83</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,7; 156,67</t>
+          <t>-57,43; 159,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,7; 724,29</t>
+          <t>-67,09; 974,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 720,44</t>
+          <t>-61,39; 749,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 213,72</t>
+          <t>-27,11; 203,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 165,93</t>
+          <t>-34,76; 155,48</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 12,94</t>
+          <t>0,77; 12,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 3,78</t>
+          <t>-5,82; 4,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,05; 12,01</t>
+          <t>1,41; 12,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 4,26</t>
+          <t>-4,3; 4,65</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,42</t>
+          <t>2,82; 10,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,09</t>
+          <t>-3,69; 3,22</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,9; 202,66</t>
+          <t>5,64; 216,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 61,13</t>
+          <t>-46,56; 78,74</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,6; 221,98</t>
+          <t>9,34; 232,08</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 85,14</t>
+          <t>-41,96; 104,87</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>20,3; 168,19</t>
+          <t>27,35; 163,49</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 49,73</t>
+          <t>-35,4; 49,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 21,11</t>
+          <t>-3,06; 22,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 5,96</t>
+          <t>-14,08; 6,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 25,3</t>
+          <t>0,27; 24,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 19,06</t>
+          <t>-2,4; 20,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 20,15</t>
+          <t>3,62; 20,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 10,27</t>
+          <t>-2,57; 11,34</t>
         </is>
       </c>
     </row>
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,53; —</t>
+          <t>7,01; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,87; —</t>
+          <t>-49,93; —</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 24,7</t>
+          <t>4,49; 23,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 10,12</t>
+          <t>-4,29; 10,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 19,8</t>
+          <t>2,38; 19,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 4,79</t>
+          <t>-6,37; 5,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,77</t>
+          <t>5,54; 18,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,76</t>
+          <t>-3,91; 5,41</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>24,3; 1564,59</t>
+          <t>22,7; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 765,8</t>
+          <t>-73,12; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,36; 1292,49</t>
+          <t>5,66; 1354,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-84,31; 353,0</t>
+          <t>-79,67; 550,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>63,83; 890,5</t>
+          <t>56,25; 783,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,58; 268,12</t>
+          <t>-56,37; 248,8</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 8,7</t>
+          <t>-25,78; 8,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 5,2</t>
+          <t>-27,12; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,43; 11,54</t>
+          <t>-20,63; 9,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,53; -1,95</t>
+          <t>-25,97; -0,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,84; 6,22</t>
+          <t>-15,65; 5,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,58; -2,59</t>
+          <t>-21,36; -1,4</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-80,99; 206,95</t>
+          <t>-82,66; 195,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-87,26; 165,76</t>
+          <t>-89,25; 125,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,43; 123,96</t>
+          <t>-73,53; 99,9</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,95; -1,4</t>
+          <t>-90,43; 1,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 70,25</t>
+          <t>-62,32; 55,29</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,97; -12,23</t>
+          <t>-83,46; -7,63</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 18,05</t>
+          <t>-5,67; 18,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,93; 11,63</t>
+          <t>-8,85; 11,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 14,98</t>
+          <t>-3,33; 13,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 12,63</t>
+          <t>-3,86; 13,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 12,17</t>
+          <t>-2,9; 12,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 8,98</t>
+          <t>-3,94; 9,37</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,09; 258,83</t>
+          <t>-38,46; 274,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 159,81</t>
+          <t>-56,11; 156,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,09; 974,91</t>
+          <t>-59,33; 700,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-61,39; 749,65</t>
+          <t>-57,0; 722,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 203,07</t>
+          <t>-24,66; 210,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,76; 155,48</t>
+          <t>-34,41; 167,03</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,77; 12,58</t>
+          <t>0,43; 12,48</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 4,45</t>
+          <t>-5,84; 4,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 12,11</t>
+          <t>1,31; 12,76</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 4,65</t>
+          <t>-4,39; 4,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,82; 10,81</t>
+          <t>2,55; 10,68</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,22</t>
+          <t>-4,04; 2,78</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>5,64; 216,23</t>
+          <t>1,69; 193,66</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,56; 78,74</t>
+          <t>-48,64; 80,72</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9,34; 232,08</t>
+          <t>10,13; 241,51</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 104,87</t>
+          <t>-43,95; 93,75</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27,35; 163,49</t>
+          <t>24,33; 172,16</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,4; 49,55</t>
+          <t>-38,64; 44,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP42B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP42B-Edad-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,94</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>11,29</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,25</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,5</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 22,83</t>
+          <t>0,58; 23,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 6,37</t>
+          <t>-3,2; 19,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 24,14</t>
+          <t>-0,68; 22,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 20,27</t>
+          <t>-11,54; 6,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,62; 20,32</t>
+          <t>3,98; 20,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 11,34</t>
+          <t>-3,08; 11,16</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>345,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>246,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>291,14%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>6,52%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>345,14%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>246,72%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,01; —</t>
+          <t>3,98; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-49,93; —</t>
+          <t>-62,77; —</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>10,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,45</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>13,64</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>3,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,95</t>
+          <t>3,08; 19,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 10,57</t>
+          <t>-6,89; 4,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 19,81</t>
+          <t>4,06; 22,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,33</t>
+          <t>-3,41; 10,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,54; 18,67</t>
+          <t>5,73; 18,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 5,41</t>
+          <t>-3,16; 5,32</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>228,72%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-9,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>319,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>72,89%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>228,72%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,7; —</t>
+          <t>20,41; 1321,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,12; —</t>
+          <t>-85,23; 354,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 1354,65</t>
+          <t>14,71; 1596,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,67; 550,18</t>
+          <t>-68,66; 750,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,25; 783,09</t>
+          <t>67,18; 786,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,37; 248,8</t>
+          <t>-52,41; 232,75</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-4,27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-12,6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-5,3</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-8,5</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,27</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-12,6</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 8,98</t>
+          <t>-19,15; 9,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-27,12; 4,72</t>
+          <t>-26,38; -1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 9,63</t>
+          <t>-27,48; 8,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,97; -0,67</t>
+          <t>-26,43; 5,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 5,44</t>
+          <t>-16,65; 5,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,36; -1,4</t>
+          <t>-21,5; -1,88</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-22,74%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-67,15%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-32,46%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-52,08%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-22,74%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-67,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,66; 195,77</t>
+          <t>-69,22; 96,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,25; 125,18</t>
+          <t>-92,29; 4,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,53; 99,9</t>
+          <t>-86,64; 194,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-90,43; 1,0</t>
+          <t>-87,58; 174,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,32; 55,29</t>
+          <t>-65,23; 56,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,46; -7,63</t>
+          <t>-84,06; -9,47</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,52</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>5,2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1,07</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,52</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,7</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 18,01</t>
+          <t>-3,03; 14,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 11,53</t>
+          <t>-2,58; 13,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 13,48</t>
+          <t>-6,39; 17,34</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 13,01</t>
+          <t>-9,83; 12,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 12,15</t>
+          <t>-2,78; 13,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,37</t>
+          <t>-4,47; 9,65</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>88,86%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>41,56%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 274,26</t>
+          <t>-60,7; 724,29</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,11; 156,41</t>
+          <t>-51,56; 720,44</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 700,36</t>
+          <t>-40,13; 247,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,0; 722,24</t>
+          <t>-57,7; 156,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 210,4</t>
+          <t>-26,7; 213,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-34,41; 167,03</t>
+          <t>-40,86; 165,93</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,72</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>6,61</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,76</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>6,72</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,43; 12,48</t>
+          <t>1,05; 12,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 4,53</t>
+          <t>-4,21; 4,26</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 12,76</t>
+          <t>0,68; 12,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 4,38</t>
+          <t>-5,97; 3,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 10,68</t>
+          <t>2,55; 10,42</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,78</t>
+          <t>-3,99; 3,09</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>91,85%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>71,93%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-8,26%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>1,69; 193,66</t>
+          <t>5,6; 221,98</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-48,64; 80,72</t>
+          <t>-43,68; 85,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10,13; 241,51</t>
+          <t>3,9; 202,66</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-43,95; 93,75</t>
+          <t>-50,08; 61,13</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>24,33; 172,16</t>
+          <t>20,3; 168,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-38,64; 44,13</t>
+          <t>-38,31; 49,73</t>
         </is>
       </c>
     </row>
